--- a/logs/nzd/raw/D10.xlsx
+++ b/logs/nzd/raw/D10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\0420\FMO\Liquidity management\Operations\Open market operations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B73186-4A82-4757-8623-758BDA8A6E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F3AFD3-9607-4293-AD19-F38FC50A4692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30450" yWindow="4380" windowWidth="38700" windowHeight="15225" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="History_C16 (to Mar 1999)" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="112">
   <si>
     <t>C16 Influences on Primary Liquidity</t>
   </si>
@@ -1315,12 +1315,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U30"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="21" width="12.81640625" style="8" customWidth="1"/>
+    <col min="2" max="21" width="12.85546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -1345,7 +1345,7 @@
       <c r="T1" s="37"/>
       <c r="U1" s="37"/>
     </row>
-    <row r="2" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1370,7 +1370,7 @@
       <c r="T2" s="12"/>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -1393,7 +1393,7 @@
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
     </row>
-    <row r="4" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="41"/>
       <c r="B4" s="22" t="s">
         <v>2</v>
@@ -1422,7 +1422,7 @@
       <c r="T4" s="23"/>
       <c r="U4" s="24"/>
     </row>
-    <row r="5" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="44"/>
       <c r="B5" s="45"/>
       <c r="C5" s="8"/>
@@ -1449,7 +1449,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="49"/>
     </row>
-    <row r="6" spans="1:21" ht="46" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="60" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
       <c r="B6" s="25" t="s">
         <v>7</v>
@@ -1512,7 +1512,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>27</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>552.61290322580646</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
         <v>35582</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>539.73333333333335</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="14">
         <v>35612</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>548.12903225806451</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="14">
         <v>35643</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>549.66359447004606</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="14">
         <v>35674</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>547.44670846394979</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
         <v>35704</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>558.68328445747795</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="14">
         <v>35735</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>562.94000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="14">
         <v>35765</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>556.54531490015358</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="14">
         <v>35796</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>571.6633333333333</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <v>35827</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>547.95676691729329</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="14">
         <v>35855</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>535.8651026392962</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>35886</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>556.66666666666674</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="14">
         <v>35916</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>549.43010752688178</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="14">
         <v>35947</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>539.76164835164832</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="14">
         <v>35977</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>552.13391304347829</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="14">
         <v>36008</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>512.91858678955452</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="14">
         <v>36039</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>535.43606060606055</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" s="14">
         <v>36069</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>552.23571428571438</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" s="14">
         <v>36100</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>495.10523809523801</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="14">
         <v>36130</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>470.81451612903209</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" s="14">
         <v>36161</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>487.94127334465173</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="17">
         <v>36192</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>539.78846428571433</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="17">
         <v>36220</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>387.97702172650742</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="L30"/>
       <c r="M30"/>
       <c r="N30"/>
@@ -3036,15 +3036,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:IS121"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="22" width="12.81640625" style="59" customWidth="1"/>
-    <col min="23" max="23" width="10.1796875" style="59" customWidth="1"/>
-    <col min="24" max="29" width="12.81640625" style="59" customWidth="1"/>
-    <col min="30" max="42" width="9.1796875" style="5" customWidth="1"/>
+    <col min="2" max="22" width="12.85546875" style="59" customWidth="1"/>
+    <col min="23" max="23" width="10.140625" style="59" customWidth="1"/>
+    <col min="24" max="29" width="12.85546875" style="59" customWidth="1"/>
+    <col min="30" max="42" width="9.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
         <v>29</v>
       </c>
@@ -3090,7 +3090,7 @@
       <c r="AO1" s="5"/>
       <c r="AP1" s="5"/>
     </row>
-    <row r="2" spans="1:42" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10"/>
       <c r="B2" s="64" t="s">
         <v>1</v>
@@ -3136,7 +3136,7 @@
       <c r="AO2" s="5"/>
       <c r="AP2" s="5"/>
     </row>
-    <row r="3" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="56"/>
       <c r="C3" s="65"/>
       <c r="D3" s="65"/>
@@ -3179,7 +3179,7 @@
       <c r="AO3" s="5"/>
       <c r="AP3" s="5"/>
     </row>
-    <row r="4" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="101" t="s">
         <v>99</v>
       </c>
@@ -3247,7 +3247,7 @@
       <c r="AO4" s="5"/>
       <c r="AP4" s="5"/>
     </row>
-    <row r="5" spans="1:42" s="1" customFormat="1" ht="46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" s="102"/>
       <c r="B5" s="96"/>
       <c r="C5" s="96"/>
@@ -3331,7 +3331,7 @@
       <c r="AO5" s="5"/>
       <c r="AP5" s="5"/>
     </row>
-    <row r="6" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="69"/>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -3374,7 +3374,7 @@
       <c r="AO6" s="5"/>
       <c r="AP6" s="5"/>
     </row>
-    <row r="7" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>53</v>
       </c>
@@ -3477,7 +3477,7 @@
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
     </row>
-    <row r="8" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>54</v>
       </c>
@@ -3580,7 +3580,7 @@
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
     </row>
-    <row r="9" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>55</v>
       </c>
@@ -3683,7 +3683,7 @@
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
     </row>
-    <row r="10" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>56</v>
       </c>
@@ -3786,7 +3786,7 @@
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
     </row>
-    <row r="11" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>57</v>
       </c>
@@ -3889,7 +3889,7 @@
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
     </row>
-    <row r="12" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>58</v>
       </c>
@@ -3992,7 +3992,7 @@
       <c r="AO12" s="5"/>
       <c r="AP12" s="5"/>
     </row>
-    <row r="13" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>59</v>
       </c>
@@ -4095,7 +4095,7 @@
       <c r="AO13" s="5"/>
       <c r="AP13" s="5"/>
     </row>
-    <row r="14" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>60</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
     </row>
-    <row r="15" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>61</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
     </row>
-    <row r="16" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>62</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
     </row>
-    <row r="17" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>63</v>
       </c>
@@ -4507,7 +4507,7 @@
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
     </row>
-    <row r="18" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>64</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>65</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>66</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>67</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="22" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="71" t="s">
         <v>68</v>
       </c>
@@ -4970,7 +4970,7 @@
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
     </row>
-    <row r="23" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="71" t="s">
         <v>69</v>
       </c>
@@ -5073,7 +5073,7 @@
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
     </row>
-    <row r="24" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="71" t="s">
         <v>70</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
     </row>
-    <row r="25" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>71</v>
       </c>
@@ -5279,7 +5279,7 @@
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
     </row>
-    <row r="26" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>72</v>
       </c>
@@ -5382,7 +5382,7 @@
       <c r="AO26" s="5"/>
       <c r="AP26" s="5"/>
     </row>
-    <row r="27" spans="1:42" s="21" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" s="21" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="72" t="s">
         <v>73</v>
       </c>
@@ -5485,7 +5485,7 @@
       <c r="AO27" s="76"/>
       <c r="AP27" s="76"/>
     </row>
-    <row r="28" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="72" t="s">
         <v>74</v>
       </c>
@@ -5588,7 +5588,7 @@
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
     </row>
-    <row r="29" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="72" t="s">
         <v>75</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="30" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="72" t="s">
         <v>76</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="72" t="s">
         <v>77</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="32" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="72" t="s">
         <v>78</v>
       </c>
@@ -5961,7 +5961,7 @@
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
     </row>
-    <row r="33" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="72" t="s">
         <v>79</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="34" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="72" t="s">
         <v>80</v>
       </c>
@@ -6154,7 +6154,7 @@
       <c r="AO34" s="5"/>
       <c r="AP34" s="5"/>
     </row>
-    <row r="35" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="72" t="s">
         <v>81</v>
       </c>
@@ -6257,7 +6257,7 @@
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
     </row>
-    <row r="36" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>82</v>
       </c>
@@ -6360,7 +6360,7 @@
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
     </row>
-    <row r="37" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>83</v>
       </c>
@@ -6463,7 +6463,7 @@
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
     </row>
-    <row r="38" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>84</v>
       </c>
@@ -6777,7 +6777,7 @@
       <c r="IR38" s="5"/>
       <c r="IS38" s="15"/>
     </row>
-    <row r="39" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>85</v>
       </c>
@@ -7091,7 +7091,7 @@
       <c r="IR39" s="5"/>
       <c r="IS39" s="15"/>
     </row>
-    <row r="40" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
         <v>86</v>
       </c>
@@ -7194,7 +7194,7 @@
       <c r="AO40" s="5"/>
       <c r="AP40" s="5"/>
     </row>
-    <row r="41" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>87</v>
       </c>
@@ -7297,7 +7297,7 @@
       <c r="AO41" s="5"/>
       <c r="AP41" s="5"/>
     </row>
-    <row r="42" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>88</v>
       </c>
@@ -7400,7 +7400,7 @@
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
     </row>
-    <row r="43" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>89</v>
       </c>
@@ -7503,7 +7503,7 @@
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
     </row>
-    <row r="44" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>90</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>3393</v>
       </c>
     </row>
-    <row r="45" spans="1:253" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:253" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>91</v>
       </c>
@@ -7696,7 +7696,7 @@
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
     </row>
-    <row r="46" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:253" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="73" t="s">
         <v>92</v>
       </c>
@@ -7799,7 +7799,7 @@
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
     </row>
-    <row r="47" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="73" t="s">
         <v>93</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>3248</v>
       </c>
     </row>
-    <row r="48" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:253" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="74">
         <v>37500</v>
       </c>
@@ -7979,7 +7979,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="49" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="74">
         <v>37530</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>4280</v>
       </c>
     </row>
-    <row r="50" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="74">
         <v>37561</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>6142</v>
       </c>
     </row>
-    <row r="51" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="75">
         <v>37591</v>
       </c>
@@ -8262,7 +8262,7 @@
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
     </row>
-    <row r="52" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="75">
         <v>37622</v>
       </c>
@@ -8355,7 +8355,7 @@
       <c r="AO52"/>
       <c r="AP52"/>
     </row>
-    <row r="53" spans="1:243" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:243" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="75">
         <v>37653</v>
       </c>
@@ -8562,7 +8562,7 @@
       <c r="IH53" s="3"/>
       <c r="II53" s="3"/>
     </row>
-    <row r="54" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="75">
         <v>37681</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>5411</v>
       </c>
     </row>
-    <row r="55" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="75">
         <v>37712</v>
       </c>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="AD55" s="5"/>
     </row>
-    <row r="56" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:243" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="75">
         <v>37742</v>
       </c>
@@ -8855,7 +8855,7 @@
       <c r="AY56" s="5"/>
       <c r="AZ56" s="5"/>
     </row>
-    <row r="57" spans="1:243" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:243" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="75">
         <v>37773</v>
       </c>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AD57" s="5"/>
     </row>
-    <row r="58" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="75">
         <v>37803</v>
       </c>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AD58" s="5"/>
     </row>
-    <row r="59" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="75">
         <v>37834</v>
       </c>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AD59" s="5"/>
     </row>
-    <row r="60" spans="1:243" s="78" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:243" s="78" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="75">
         <v>37866</v>
       </c>
@@ -9221,7 +9221,7 @@
       <c r="AO60" s="76"/>
       <c r="AP60" s="76"/>
     </row>
-    <row r="61" spans="1:243" s="79" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:243" s="79" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="75">
         <v>37895</v>
       </c>
@@ -9314,7 +9314,7 @@
       <c r="AO61" s="76"/>
       <c r="AP61" s="76"/>
     </row>
-    <row r="62" spans="1:243" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:243" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="75">
         <v>37926</v>
       </c>
@@ -9417,7 +9417,7 @@
       <c r="AO62" s="5"/>
       <c r="AP62" s="5"/>
     </row>
-    <row r="63" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="75">
         <v>37956</v>
       </c>
@@ -9520,7 +9520,7 @@
       <c r="AO63" s="5"/>
       <c r="AP63" s="5"/>
     </row>
-    <row r="64" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:243" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="75">
         <v>37987</v>
       </c>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AD64" s="5"/>
     </row>
-    <row r="65" spans="1:42" s="82" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" s="82" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="75">
         <v>38018</v>
       </c>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="AD65" s="5"/>
     </row>
-    <row r="66" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="75">
         <v>38047</v>
       </c>
@@ -9805,7 +9805,7 @@
       <c r="AO66" s="5"/>
       <c r="AP66" s="5"/>
     </row>
-    <row r="67" spans="1:42" s="21" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" s="21" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="75">
         <v>38078</v>
       </c>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AD67" s="5"/>
     </row>
-    <row r="68" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="75">
         <v>38108</v>
       </c>
@@ -9991,7 +9991,7 @@
       <c r="AH68" s="5"/>
       <c r="AP68" s="5"/>
     </row>
-    <row r="69" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="75">
         <v>38139</v>
       </c>
@@ -10091,7 +10091,7 @@
       <c r="AL69" s="5"/>
       <c r="AM69" s="5"/>
     </row>
-    <row r="70" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="75">
         <v>38169</v>
       </c>
@@ -10194,7 +10194,7 @@
       <c r="AO70" s="5"/>
       <c r="AP70" s="5"/>
     </row>
-    <row r="71" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="75">
         <v>38200</v>
       </c>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="AD71" s="5"/>
     </row>
-    <row r="72" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="75">
         <v>38231</v>
       </c>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AD72" s="5"/>
     </row>
-    <row r="73" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="75">
         <v>38261</v>
       </c>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="AD73" s="5"/>
     </row>
-    <row r="74" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="75">
         <v>38292</v>
       </c>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="AD74" s="5"/>
     </row>
-    <row r="75" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="75">
         <v>38322</v>
       </c>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="AD75" s="5"/>
     </row>
-    <row r="76" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="75">
         <v>38353</v>
       </c>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AD76" s="5"/>
     </row>
-    <row r="77" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="75">
         <v>38384</v>
       </c>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="AD77" s="5"/>
     </row>
-    <row r="78" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="75">
         <v>38412</v>
       </c>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="AD78" s="5"/>
     </row>
-    <row r="79" spans="1:42" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:42" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="75">
         <v>38443</v>
       </c>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="AD79" s="5"/>
     </row>
-    <row r="80" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:42" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="75">
         <v>38473</v>
       </c>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AD80" s="5"/>
     </row>
-    <row r="81" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="75">
         <v>38504</v>
       </c>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AD81" s="5"/>
     </row>
-    <row r="82" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="75">
         <v>38534</v>
       </c>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="AD82" s="5"/>
     </row>
-    <row r="83" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="75">
         <v>38565</v>
       </c>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AD83" s="5"/>
     </row>
-    <row r="84" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="75">
         <v>38596</v>
       </c>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="AD84" s="5"/>
     </row>
-    <row r="85" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="75">
         <v>38626</v>
       </c>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="AD85" s="5"/>
     </row>
-    <row r="86" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="75">
         <v>38657</v>
       </c>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="AD86" s="5"/>
     </row>
-    <row r="87" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="75">
         <v>38687</v>
       </c>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="AD87" s="5"/>
     </row>
-    <row r="88" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="75">
         <v>38718</v>
       </c>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="AD88" s="5"/>
     </row>
-    <row r="89" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="75">
         <v>38749</v>
       </c>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="AD89" s="5"/>
     </row>
-    <row r="90" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="75">
         <v>38777</v>
       </c>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="AD90" s="5"/>
     </row>
-    <row r="91" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="75">
         <v>38808</v>
       </c>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="AD91" s="5"/>
     </row>
-    <row r="92" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="75">
         <v>38838</v>
       </c>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="AD92" s="5"/>
     </row>
-    <row r="93" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="75">
         <v>38869</v>
       </c>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="AD93" s="5"/>
     </row>
-    <row r="94" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="75">
         <v>38899</v>
       </c>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="AD94" s="5"/>
     </row>
-    <row r="95" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="75">
         <v>38930</v>
       </c>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AD95" s="5"/>
     </row>
-    <row r="96" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="75">
         <v>38961</v>
       </c>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="AD96" s="5"/>
     </row>
-    <row r="97" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="75">
         <v>38991</v>
       </c>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="AD97" s="5"/>
     </row>
-    <row r="98" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="75">
         <v>39022</v>
       </c>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="AD98" s="5"/>
     </row>
-    <row r="99" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="75">
         <v>39052</v>
       </c>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="AD99" s="5"/>
     </row>
-    <row r="100" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="75">
         <v>39083</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AD100" s="5"/>
     </row>
-    <row r="101" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="75">
         <v>39114</v>
       </c>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AD101" s="5"/>
     </row>
-    <row r="102" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="75">
         <v>39142</v>
       </c>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="AD102" s="5"/>
     </row>
-    <row r="103" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="75">
         <v>39173</v>
       </c>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="AD103" s="5"/>
     </row>
-    <row r="104" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="75">
         <v>39203</v>
       </c>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="AD104" s="5"/>
     </row>
-    <row r="105" spans="1:30" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="75">
         <v>39234</v>
       </c>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="AD105" s="5"/>
     </row>
-    <row r="106" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="75">
         <v>39264</v>
       </c>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="AD106" s="5"/>
     </row>
-    <row r="107" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="75">
         <v>39295</v>
       </c>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AD107" s="5"/>
     </row>
-    <row r="108" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="75">
         <v>39326</v>
       </c>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AD108" s="5"/>
     </row>
-    <row r="109" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="75">
         <v>39356</v>
       </c>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="AD109" s="5"/>
     </row>
-    <row r="110" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="75">
         <v>39387</v>
       </c>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="AD110" s="5"/>
     </row>
-    <row r="111" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="75">
         <v>39417</v>
       </c>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="AD111" s="5"/>
     </row>
-    <row r="112" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="75"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -13957,7 +13957,7 @@
       <c r="AC112" s="5"/>
       <c r="AD112" s="5"/>
     </row>
-    <row r="113" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="75"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -13989,7 +13989,7 @@
       <c r="AC113" s="5"/>
       <c r="AD113" s="5"/>
     </row>
-    <row r="114" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="75"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -14021,7 +14021,7 @@
       <c r="AC114" s="5"/>
       <c r="AD114" s="5"/>
     </row>
-    <row r="115" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="75"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -14053,7 +14053,7 @@
       <c r="AC115" s="5"/>
       <c r="AD115" s="5"/>
     </row>
-    <row r="116" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="75"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -14085,7 +14085,7 @@
       <c r="AC116" s="5"/>
       <c r="AD116" s="5"/>
     </row>
-    <row r="117" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="75"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -14117,7 +14117,7 @@
       <c r="AC117" s="5"/>
       <c r="AD117" s="5"/>
     </row>
-    <row r="118" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="75"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -14149,7 +14149,7 @@
       <c r="AC118" s="5"/>
       <c r="AD118" s="5"/>
     </row>
-    <row r="119" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="75"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -14181,7 +14181,7 @@
       <c r="AC119" s="5"/>
       <c r="AD119" s="5"/>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A120" s="75"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -14212,7 +14212,7 @@
       <c r="AB120" s="5"/>
       <c r="AC120" s="5"/>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A121" s="84"/>
       <c r="B121" s="76"/>
       <c r="C121" s="76"/>
@@ -14271,19 +14271,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:IY229"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:IY230"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="25" width="12.81640625" style="59" customWidth="1"/>
-    <col min="26" max="26" width="10.1796875" style="59" customWidth="1"/>
-    <col min="27" max="35" width="12.81640625" style="59" customWidth="1"/>
-    <col min="36" max="36" width="10.54296875" style="5" customWidth="1"/>
-    <col min="37" max="39" width="9.1796875" style="5" customWidth="1"/>
-    <col min="40" max="40" width="9.1796875" style="85" customWidth="1"/>
-    <col min="41" max="48" width="9.1796875" style="5" customWidth="1"/>
+    <col min="2" max="25" width="12.85546875" style="59" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" style="59" customWidth="1"/>
+    <col min="27" max="35" width="12.85546875" style="59" customWidth="1"/>
+    <col min="36" max="36" width="10.5703125" style="5" customWidth="1"/>
+    <col min="37" max="39" width="9.140625" style="5" customWidth="1"/>
+    <col min="40" max="40" width="9.140625" style="85" customWidth="1"/>
+    <col min="41" max="48" width="9.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="70" t="s">
         <v>29</v>
       </c>
@@ -14335,7 +14335,7 @@
       <c r="AU1" s="5"/>
       <c r="AV1" s="5"/>
     </row>
-    <row r="2" spans="1:48" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10"/>
       <c r="B2" s="64" t="s">
         <v>1</v>
@@ -14387,7 +14387,7 @@
       <c r="AU2" s="5"/>
       <c r="AV2" s="5"/>
     </row>
-    <row r="3" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="56"/>
       <c r="C3" s="65"/>
       <c r="D3" s="65"/>
@@ -14436,7 +14436,7 @@
       <c r="AU3" s="5"/>
       <c r="AV3" s="5"/>
     </row>
-    <row r="4" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="98" t="s">
         <v>99</v>
       </c>
@@ -14510,7 +14510,7 @@
       <c r="AU4" s="5"/>
       <c r="AV4" s="5"/>
     </row>
-    <row r="5" spans="1:48" s="1" customFormat="1" ht="46" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" s="99"/>
       <c r="B5" s="96"/>
       <c r="C5" s="96"/>
@@ -14612,7 +14612,7 @@
       <c r="AU5" s="5"/>
       <c r="AV5" s="5"/>
     </row>
-    <row r="6" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="69"/>
       <c r="C6" s="58"/>
       <c r="D6" s="58"/>
@@ -14661,7 +14661,7 @@
       <c r="AU6" s="5"/>
       <c r="AV6" s="5"/>
     </row>
-    <row r="7" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="75">
         <v>39448</v>
       </c>
@@ -14769,7 +14769,7 @@
       <c r="AU7" s="5"/>
       <c r="AV7" s="5"/>
     </row>
-    <row r="8" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="75">
         <v>39479</v>
       </c>
@@ -14877,7 +14877,7 @@
       <c r="AU8" s="5"/>
       <c r="AV8" s="5"/>
     </row>
-    <row r="9" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="75">
         <v>39508</v>
       </c>
@@ -14985,7 +14985,7 @@
       <c r="AU9" s="5"/>
       <c r="AV9" s="5"/>
     </row>
-    <row r="10" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="75">
         <v>39539</v>
       </c>
@@ -15093,7 +15093,7 @@
       <c r="AU10" s="5"/>
       <c r="AV10" s="5"/>
     </row>
-    <row r="11" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="75">
         <v>39569</v>
       </c>
@@ -15201,7 +15201,7 @@
       <c r="AU11" s="5"/>
       <c r="AV11" s="5"/>
     </row>
-    <row r="12" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="75">
         <v>39600</v>
       </c>
@@ -15309,7 +15309,7 @@
       <c r="AU12" s="5"/>
       <c r="AV12" s="5"/>
     </row>
-    <row r="13" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="75">
         <v>39630</v>
       </c>
@@ -15417,7 +15417,7 @@
       <c r="AU13" s="5"/>
       <c r="AV13" s="5"/>
     </row>
-    <row r="14" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="75">
         <v>39661</v>
       </c>
@@ -15525,7 +15525,7 @@
       <c r="AU14" s="5"/>
       <c r="AV14" s="5"/>
     </row>
-    <row r="15" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="75">
         <v>39692</v>
       </c>
@@ -15633,7 +15633,7 @@
       <c r="AU15" s="5"/>
       <c r="AV15" s="5"/>
     </row>
-    <row r="16" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="75">
         <v>39722</v>
       </c>
@@ -15741,7 +15741,7 @@
       <c r="AU16" s="5"/>
       <c r="AV16" s="5"/>
     </row>
-    <row r="17" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="75">
         <v>39753</v>
       </c>
@@ -15849,7 +15849,7 @@
       <c r="AU17" s="5"/>
       <c r="AV17" s="5"/>
     </row>
-    <row r="18" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="75">
         <v>39783</v>
       </c>
@@ -15944,7 +15944,7 @@
         <v>7070.172999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="75">
         <v>39814</v>
       </c>
@@ -16039,7 +16039,7 @@
         <v>12461.466</v>
       </c>
     </row>
-    <row r="20" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="75">
         <v>39845</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>13570.315999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="75">
         <v>39873</v>
       </c>
@@ -16242,7 +16242,7 @@
       <c r="AU21" s="5"/>
       <c r="AV21" s="5"/>
     </row>
-    <row r="22" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="75">
         <v>39904</v>
       </c>
@@ -16350,7 +16350,7 @@
       <c r="AU22" s="5"/>
       <c r="AV22" s="5"/>
     </row>
-    <row r="23" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="75">
         <v>39934</v>
       </c>
@@ -16458,7 +16458,7 @@
       <c r="AU23" s="5"/>
       <c r="AV23" s="5"/>
     </row>
-    <row r="24" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="75">
         <v>39965</v>
       </c>
@@ -16566,7 +16566,7 @@
       <c r="AU24" s="5"/>
       <c r="AV24" s="5"/>
     </row>
-    <row r="25" spans="1:48" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="75">
         <v>39995</v>
       </c>
@@ -16666,7 +16666,7 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="85"/>
     </row>
-    <row r="26" spans="1:48" s="21" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" s="21" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="75">
         <v>40026</v>
       </c>
@@ -16774,7 +16774,7 @@
       <c r="AU26" s="76"/>
       <c r="AV26" s="76"/>
     </row>
-    <row r="27" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="75">
         <v>40057</v>
       </c>
@@ -16882,7 +16882,7 @@
       <c r="AU27" s="5"/>
       <c r="AV27" s="5"/>
     </row>
-    <row r="28" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="75">
         <v>40087</v>
       </c>
@@ -16977,7 +16977,7 @@
         <v>14846.740215139998</v>
       </c>
     </row>
-    <row r="29" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="75">
         <v>40118</v>
       </c>
@@ -17072,7 +17072,7 @@
         <v>14600.80221514</v>
       </c>
     </row>
-    <row r="30" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="75">
         <v>40148</v>
       </c>
@@ -17167,7 +17167,7 @@
         <v>12068.292215139998</v>
       </c>
     </row>
-    <row r="31" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="75">
         <v>40179</v>
       </c>
@@ -17275,7 +17275,7 @@
       <c r="AU31" s="5"/>
       <c r="AV31" s="5"/>
     </row>
-    <row r="32" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="75">
         <v>40210</v>
       </c>
@@ -17370,7 +17370,7 @@
         <v>12836.000215139999</v>
       </c>
     </row>
-    <row r="33" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="75">
         <v>40238</v>
       </c>
@@ -17478,7 +17478,7 @@
       <c r="AU33" s="5"/>
       <c r="AV33" s="5"/>
     </row>
-    <row r="34" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="75">
         <v>40269</v>
       </c>
@@ -17586,7 +17586,7 @@
       <c r="AU34" s="5"/>
       <c r="AV34" s="5"/>
     </row>
-    <row r="35" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="75">
         <v>40299</v>
       </c>
@@ -17694,7 +17694,7 @@
       <c r="AU35" s="5"/>
       <c r="AV35" s="5"/>
     </row>
-    <row r="36" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="75">
         <v>40330</v>
       </c>
@@ -17802,7 +17802,7 @@
       <c r="AU36" s="5"/>
       <c r="AV36" s="5"/>
     </row>
-    <row r="37" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="75">
         <v>40360</v>
       </c>
@@ -18121,7 +18121,7 @@
       <c r="IX37" s="5"/>
       <c r="IY37" s="15"/>
     </row>
-    <row r="38" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="75">
         <v>40391</v>
       </c>
@@ -18440,7 +18440,7 @@
       <c r="IX38" s="5"/>
       <c r="IY38" s="15"/>
     </row>
-    <row r="39" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="75">
         <v>40422</v>
       </c>
@@ -18548,7 +18548,7 @@
       <c r="AU39" s="5"/>
       <c r="AV39" s="5"/>
     </row>
-    <row r="40" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="75">
         <v>40452</v>
       </c>
@@ -18656,7 +18656,7 @@
       <c r="AU40" s="5"/>
       <c r="AV40" s="5"/>
     </row>
-    <row r="41" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="75">
         <v>40483</v>
       </c>
@@ -18764,7 +18764,7 @@
       <c r="AU41" s="5"/>
       <c r="AV41" s="5"/>
     </row>
-    <row r="42" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:259" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="75">
         <v>40513</v>
       </c>
@@ -18872,7 +18872,7 @@
       <c r="AU42" s="5"/>
       <c r="AV42" s="5"/>
     </row>
-    <row r="43" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="75">
         <v>40544</v>
       </c>
@@ -18967,7 +18967,7 @@
         <v>14566.879999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:259" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:259" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="75">
         <v>40575</v>
       </c>
@@ -19075,7 +19075,7 @@
       <c r="AU44" s="5"/>
       <c r="AV44" s="5"/>
     </row>
-    <row r="45" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="75">
         <v>40603</v>
       </c>
@@ -19170,7 +19170,7 @@
         <v>15750.218000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="75">
         <v>40634</v>
       </c>
@@ -19265,7 +19265,7 @@
         <v>17459.476000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="75">
         <v>40664</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>19706.426000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:259" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="75">
         <v>40695</v>
       </c>
@@ -19455,7 +19455,7 @@
         <v>20529.925000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="75">
         <v>40725</v>
       </c>
@@ -19563,7 +19563,7 @@
       <c r="AU49" s="5"/>
       <c r="AV49" s="5"/>
     </row>
-    <row r="50" spans="1:249" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:249" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="75">
         <v>40756</v>
       </c>
@@ -19661,7 +19661,7 @@
       <c r="AU50"/>
       <c r="AV50"/>
     </row>
-    <row r="51" spans="1:249" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:249" s="9" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="75">
         <v>40787</v>
       </c>
@@ -19874,7 +19874,7 @@
       <c r="IN51" s="3"/>
       <c r="IO51" s="3"/>
     </row>
-    <row r="52" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="75">
         <v>40817</v>
       </c>
@@ -19974,7 +19974,7 @@
       <c r="AM52" s="5"/>
       <c r="AN52" s="85"/>
     </row>
-    <row r="53" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="75">
         <v>40848</v>
       </c>
@@ -20074,7 +20074,7 @@
       <c r="AM53" s="5"/>
       <c r="AN53" s="85"/>
     </row>
-    <row r="54" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="75">
         <v>40878</v>
       </c>
@@ -20174,7 +20174,7 @@
       <c r="AM54" s="5"/>
       <c r="AN54" s="85"/>
     </row>
-    <row r="55" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="75">
         <v>40909</v>
       </c>
@@ -20274,7 +20274,7 @@
       <c r="AM55" s="5"/>
       <c r="AN55" s="85"/>
     </row>
-    <row r="56" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="75">
         <v>40940</v>
       </c>
@@ -20374,7 +20374,7 @@
       <c r="AM56" s="5"/>
       <c r="AN56" s="85"/>
     </row>
-    <row r="57" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="75">
         <v>40969</v>
       </c>
@@ -20474,7 +20474,7 @@
       <c r="AM57" s="5"/>
       <c r="AN57" s="85"/>
     </row>
-    <row r="58" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="75">
         <v>41000</v>
       </c>
@@ -20574,7 +20574,7 @@
       <c r="AM58" s="5"/>
       <c r="AN58" s="85"/>
     </row>
-    <row r="59" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="75">
         <v>41030</v>
       </c>
@@ -20674,7 +20674,7 @@
       <c r="AM59" s="5"/>
       <c r="AN59" s="85"/>
     </row>
-    <row r="60" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="75">
         <v>41061</v>
       </c>
@@ -20774,7 +20774,7 @@
       <c r="AM60" s="5"/>
       <c r="AN60" s="85"/>
     </row>
-    <row r="61" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:249" s="81" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="75">
         <v>41091</v>
       </c>
@@ -20874,7 +20874,7 @@
       <c r="AM61" s="5"/>
       <c r="AN61" s="85"/>
     </row>
-    <row r="62" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="75">
         <v>41122</v>
       </c>
@@ -20979,7 +20979,7 @@
       <c r="AR62" s="5"/>
       <c r="AS62" s="5"/>
     </row>
-    <row r="63" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="75">
         <v>41153</v>
       </c>
@@ -21079,7 +21079,7 @@
       <c r="AM63" s="5"/>
       <c r="AN63" s="85"/>
     </row>
-    <row r="64" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:249" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="75">
         <v>41183</v>
       </c>
@@ -21179,7 +21179,7 @@
       <c r="AM64" s="5"/>
       <c r="AN64" s="85"/>
     </row>
-    <row r="65" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="75">
         <v>41214</v>
       </c>
@@ -21279,7 +21279,7 @@
       <c r="AM65" s="5"/>
       <c r="AN65" s="85"/>
     </row>
-    <row r="66" spans="1:40" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:40" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="75">
         <v>41244</v>
       </c>
@@ -21379,7 +21379,7 @@
       <c r="AM66" s="5"/>
       <c r="AN66" s="85"/>
     </row>
-    <row r="67" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="75">
         <v>41275</v>
       </c>
@@ -21479,7 +21479,7 @@
       <c r="AM67" s="5"/>
       <c r="AN67" s="85"/>
     </row>
-    <row r="68" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="75">
         <v>41306</v>
       </c>
@@ -21579,7 +21579,7 @@
       <c r="AM68" s="5"/>
       <c r="AN68" s="85"/>
     </row>
-    <row r="69" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="75">
         <v>41334</v>
       </c>
@@ -21679,7 +21679,7 @@
       <c r="AM69" s="5"/>
       <c r="AN69" s="85"/>
     </row>
-    <row r="70" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="75">
         <v>41365</v>
       </c>
@@ -21779,7 +21779,7 @@
       <c r="AM70" s="5"/>
       <c r="AN70" s="85"/>
     </row>
-    <row r="71" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="75">
         <v>41395</v>
       </c>
@@ -21879,7 +21879,7 @@
       <c r="AM71" s="5"/>
       <c r="AN71" s="85"/>
     </row>
-    <row r="72" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="75">
         <v>41426</v>
       </c>
@@ -21979,7 +21979,7 @@
       <c r="AM72" s="5"/>
       <c r="AN72" s="85"/>
     </row>
-    <row r="73" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="75">
         <v>41456</v>
       </c>
@@ -22079,7 +22079,7 @@
       <c r="AM73" s="5"/>
       <c r="AN73" s="85"/>
     </row>
-    <row r="74" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="75">
         <v>41487</v>
       </c>
@@ -22179,7 +22179,7 @@
       <c r="AM74" s="5"/>
       <c r="AN74" s="85"/>
     </row>
-    <row r="75" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="75">
         <v>41518</v>
       </c>
@@ -22279,7 +22279,7 @@
       <c r="AM75" s="5"/>
       <c r="AN75" s="85"/>
     </row>
-    <row r="76" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="75">
         <v>41548</v>
       </c>
@@ -22379,7 +22379,7 @@
       <c r="AM76" s="5"/>
       <c r="AN76" s="85"/>
     </row>
-    <row r="77" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="75">
         <v>41579</v>
       </c>
@@ -22479,7 +22479,7 @@
       <c r="AM77" s="5"/>
       <c r="AN77" s="85"/>
     </row>
-    <row r="78" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="75">
         <v>41609</v>
       </c>
@@ -22579,7 +22579,7 @@
       <c r="AM78" s="5"/>
       <c r="AN78" s="85"/>
     </row>
-    <row r="79" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="75">
         <v>41640</v>
       </c>
@@ -22679,7 +22679,7 @@
       <c r="AM79" s="5"/>
       <c r="AN79" s="85"/>
     </row>
-    <row r="80" spans="1:40" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:40" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="75">
         <v>41671</v>
       </c>
@@ -22779,7 +22779,7 @@
       <c r="AM80" s="5"/>
       <c r="AN80" s="85"/>
     </row>
-    <row r="81" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="75">
         <v>41699</v>
       </c>
@@ -22879,7 +22879,7 @@
       <c r="AM81" s="5"/>
       <c r="AN81" s="85"/>
     </row>
-    <row r="82" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="75">
         <v>41730</v>
       </c>
@@ -22979,7 +22979,7 @@
       <c r="AM82" s="5"/>
       <c r="AN82" s="85"/>
     </row>
-    <row r="83" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="75">
         <v>41760</v>
       </c>
@@ -23079,7 +23079,7 @@
       <c r="AM83" s="5"/>
       <c r="AN83" s="85"/>
     </row>
-    <row r="84" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="75">
         <v>41791</v>
       </c>
@@ -23179,7 +23179,7 @@
       <c r="AM84" s="5"/>
       <c r="AN84" s="85"/>
     </row>
-    <row r="85" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="75">
         <v>41821</v>
       </c>
@@ -23279,7 +23279,7 @@
       <c r="AM85" s="5"/>
       <c r="AN85" s="85"/>
     </row>
-    <row r="86" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="75">
         <v>41852</v>
       </c>
@@ -23379,7 +23379,7 @@
       <c r="AM86" s="5"/>
       <c r="AN86" s="85"/>
     </row>
-    <row r="87" spans="1:40" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:40" s="80" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="75">
         <v>41883</v>
       </c>
@@ -23479,7 +23479,7 @@
       <c r="AM87" s="5"/>
       <c r="AN87" s="85"/>
     </row>
-    <row r="88" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="75">
         <v>41913</v>
       </c>
@@ -23579,7 +23579,7 @@
       <c r="AM88" s="5"/>
       <c r="AN88" s="85"/>
     </row>
-    <row r="89" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="75">
         <v>41971</v>
       </c>
@@ -23679,7 +23679,7 @@
       <c r="AM89" s="5"/>
       <c r="AN89" s="85"/>
     </row>
-    <row r="90" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="75">
         <v>42004</v>
       </c>
@@ -23779,7 +23779,7 @@
       <c r="AM90" s="5"/>
       <c r="AN90" s="85"/>
     </row>
-    <row r="91" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="75">
         <v>42034</v>
       </c>
@@ -23879,7 +23879,7 @@
       <c r="AM91" s="5"/>
       <c r="AN91" s="85"/>
     </row>
-    <row r="92" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="75">
         <v>42062</v>
       </c>
@@ -23979,7 +23979,7 @@
       <c r="AM92" s="5"/>
       <c r="AN92" s="85"/>
     </row>
-    <row r="93" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="75">
         <v>42094</v>
       </c>
@@ -24079,7 +24079,7 @@
       <c r="AM93" s="5"/>
       <c r="AN93" s="85"/>
     </row>
-    <row r="94" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="75">
         <v>42124</v>
       </c>
@@ -24179,7 +24179,7 @@
       <c r="AM94" s="5"/>
       <c r="AN94" s="85"/>
     </row>
-    <row r="95" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="75">
         <v>42153</v>
       </c>
@@ -24279,7 +24279,7 @@
       <c r="AM95" s="5"/>
       <c r="AN95" s="85"/>
     </row>
-    <row r="96" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:40" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="75">
         <v>42185</v>
       </c>
@@ -24379,7 +24379,7 @@
       <c r="AM96" s="5"/>
       <c r="AN96" s="85"/>
     </row>
-    <row r="97" spans="1:41" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:41" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="75">
         <v>42216</v>
       </c>
@@ -24479,7 +24479,7 @@
       <c r="AM97" s="5"/>
       <c r="AN97" s="85"/>
     </row>
-    <row r="98" spans="1:41" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:41" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="75">
         <v>42247</v>
       </c>
@@ -24579,7 +24579,7 @@
       <c r="AM98" s="5"/>
       <c r="AN98" s="85"/>
     </row>
-    <row r="99" spans="1:41" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:41" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="75">
         <v>42277</v>
       </c>
@@ -24679,7 +24679,7 @@
       <c r="AM99" s="5"/>
       <c r="AN99" s="85"/>
     </row>
-    <row r="100" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A100" s="75">
         <v>42307</v>
       </c>
@@ -24774,7 +24774,7 @@
         <v>14570</v>
       </c>
     </row>
-    <row r="101" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A101" s="75">
         <v>42338</v>
       </c>
@@ -24869,7 +24869,7 @@
         <v>13137</v>
       </c>
     </row>
-    <row r="102" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A102" s="75">
         <v>42369</v>
       </c>
@@ -24964,7 +24964,7 @@
         <v>12718</v>
       </c>
     </row>
-    <row r="103" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A103" s="75">
         <v>42398</v>
       </c>
@@ -25059,7 +25059,7 @@
         <v>16023</v>
       </c>
     </row>
-    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A104" s="75">
         <v>42429</v>
       </c>
@@ -25155,7 +25155,7 @@
       </c>
       <c r="AO104" s="86"/>
     </row>
-    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A105" s="75">
         <v>42460</v>
       </c>
@@ -25250,7 +25250,7 @@
         <v>12787</v>
       </c>
     </row>
-    <row r="106" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A106" s="75">
         <v>42489</v>
       </c>
@@ -25345,7 +25345,7 @@
         <v>13532</v>
       </c>
     </row>
-    <row r="107" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A107" s="75">
         <v>42521</v>
       </c>
@@ -25440,7 +25440,7 @@
         <v>16297</v>
       </c>
     </row>
-    <row r="108" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A108" s="75">
         <v>42551</v>
       </c>
@@ -25535,7 +25535,7 @@
         <v>15680</v>
       </c>
     </row>
-    <row r="109" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A109" s="75">
         <v>42580</v>
       </c>
@@ -25630,7 +25630,7 @@
         <v>13543</v>
       </c>
     </row>
-    <row r="110" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A110" s="75">
         <v>42613</v>
       </c>
@@ -25725,7 +25725,7 @@
         <v>16812</v>
       </c>
     </row>
-    <row r="111" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A111" s="75">
         <v>42643</v>
       </c>
@@ -25820,7 +25820,7 @@
         <v>15353</v>
       </c>
     </row>
-    <row r="112" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A112" s="75">
         <v>42674</v>
       </c>
@@ -25915,7 +25915,7 @@
         <v>15610</v>
       </c>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A113" s="75">
         <v>42704</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>14616</v>
       </c>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A114" s="75">
         <v>42734</v>
       </c>
@@ -26105,7 +26105,7 @@
         <v>13843</v>
       </c>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A115" s="75">
         <v>42766</v>
       </c>
@@ -26200,7 +26200,7 @@
         <v>16506</v>
       </c>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A116" s="75">
         <v>42794</v>
       </c>
@@ -26295,7 +26295,7 @@
         <v>16051</v>
       </c>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A117" s="75">
         <v>42825</v>
       </c>
@@ -26390,7 +26390,7 @@
         <v>16548</v>
       </c>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A118" s="75">
         <v>42853</v>
       </c>
@@ -26485,7 +26485,7 @@
         <v>14364</v>
       </c>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A119" s="75">
         <v>42886</v>
       </c>
@@ -26580,7 +26580,7 @@
         <v>16335</v>
       </c>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A120" s="75">
         <v>42916</v>
       </c>
@@ -26675,7 +26675,7 @@
         <v>17203</v>
       </c>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A121" s="75">
         <v>42947</v>
       </c>
@@ -26770,7 +26770,7 @@
         <v>13831.31</v>
       </c>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A122" s="75">
         <v>42978</v>
       </c>
@@ -26865,7 +26865,7 @@
         <v>16920</v>
       </c>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A123" s="75">
         <v>43007</v>
       </c>
@@ -26960,7 +26960,7 @@
         <v>16106</v>
       </c>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A124" s="75">
         <v>43039</v>
       </c>
@@ -27055,7 +27055,7 @@
         <v>17710</v>
       </c>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A125" s="75">
         <v>43069</v>
       </c>
@@ -27150,7 +27150,7 @@
         <v>16707</v>
       </c>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A126" s="75">
         <v>43098</v>
       </c>
@@ -27245,7 +27245,7 @@
         <v>16062</v>
       </c>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A127" s="75">
         <v>43131</v>
       </c>
@@ -27340,7 +27340,7 @@
         <v>19542.349999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A128" s="75">
         <v>43159</v>
       </c>
@@ -27435,7 +27435,7 @@
         <v>20109</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A129" s="75">
         <v>43188</v>
       </c>
@@ -27530,7 +27530,7 @@
         <v>19742</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A130" s="75">
         <v>43220</v>
       </c>
@@ -27625,7 +27625,7 @@
         <v>17432</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A131" s="75">
         <v>43251</v>
       </c>
@@ -27720,7 +27720,7 @@
         <v>21088</v>
       </c>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A132" s="75">
         <v>43280</v>
       </c>
@@ -27815,7 +27815,7 @@
         <v>21304</v>
       </c>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A133" s="75">
         <v>43312</v>
       </c>
@@ -27910,7 +27910,7 @@
         <v>17588</v>
       </c>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A134" s="75">
         <v>43343</v>
       </c>
@@ -28005,7 +28005,7 @@
         <v>19460</v>
       </c>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A135" s="75">
         <v>43371</v>
       </c>
@@ -28100,7 +28100,7 @@
         <v>18756</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A136" s="75">
         <v>43404</v>
       </c>
@@ -28195,7 +28195,7 @@
         <v>18106</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A137" s="75">
         <v>43434</v>
       </c>
@@ -28290,7 +28290,7 @@
         <v>18655</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A138" s="75">
         <v>43465</v>
       </c>
@@ -28385,7 +28385,7 @@
         <v>17542</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A139" s="75">
         <v>43496</v>
       </c>
@@ -28480,7 +28480,7 @@
         <v>21427</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A140" s="75">
         <v>43524</v>
       </c>
@@ -28575,7 +28575,7 @@
         <v>22730</v>
       </c>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A141" s="75">
         <v>43553</v>
       </c>
@@ -28670,7 +28670,7 @@
         <v>17366</v>
       </c>
     </row>
-    <row r="142" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A142" s="75">
         <v>43585</v>
       </c>
@@ -28765,7 +28765,7 @@
         <v>15290</v>
       </c>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A143" s="75">
         <v>43616</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>18371</v>
       </c>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A144" s="75">
         <v>43644</v>
       </c>
@@ -28955,7 +28955,7 @@
         <v>17499</v>
       </c>
     </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A145" s="75">
         <v>43677</v>
       </c>
@@ -29050,7 +29050,7 @@
         <v>15238.849999999999</v>
       </c>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A146" s="75">
         <v>43707</v>
       </c>
@@ -29145,7 +29145,7 @@
         <v>17176</v>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A147" s="75">
         <v>43738</v>
       </c>
@@ -29240,7 +29240,7 @@
         <v>16456</v>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A148" s="75">
         <v>43769</v>
       </c>
@@ -29335,7 +29335,7 @@
         <v>15128</v>
       </c>
     </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A149" s="75">
         <v>43798</v>
       </c>
@@ -29430,7 +29430,7 @@
         <v>15562</v>
       </c>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A150" s="75">
         <v>43830</v>
       </c>
@@ -29525,7 +29525,7 @@
         <v>15014</v>
       </c>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A151" s="75">
         <v>43861</v>
       </c>
@@ -29620,7 +29620,7 @@
         <v>19719</v>
       </c>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A152" s="75">
         <v>43889</v>
       </c>
@@ -29715,7 +29715,7 @@
         <v>18843</v>
       </c>
     </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A153" s="75">
         <v>43921</v>
       </c>
@@ -29814,7 +29814,7 @@
         <v>28396</v>
       </c>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A154" s="75">
         <v>43951</v>
       </c>
@@ -29913,7 +29913,7 @@
         <v>30816</v>
       </c>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A155" s="75">
         <v>43980</v>
       </c>
@@ -30016,7 +30016,7 @@
         <v>36098.042471102453</v>
       </c>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A156" s="75">
         <v>44012</v>
       </c>
@@ -30119,7 +30119,7 @@
         <v>40673.086396332932</v>
       </c>
     </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A157" s="75">
         <v>44043</v>
       </c>
@@ -30222,7 +30222,7 @@
         <v>42071.262554939996</v>
       </c>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A158" s="75">
         <v>44074</v>
       </c>
@@ -30325,7 +30325,7 @@
         <v>41159.364271750004</v>
       </c>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A159" s="75">
         <v>44104</v>
       </c>
@@ -30428,7 +30428,7 @@
         <v>43542.502524640004</v>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A160" s="75">
         <v>44134</v>
       </c>
@@ -30531,7 +30531,7 @@
         <v>46508.729999999996</v>
       </c>
     </row>
-    <row r="161" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A161" s="75">
         <v>44165</v>
       </c>
@@ -30634,7 +30634,7 @@
         <v>50323.683240700004</v>
       </c>
     </row>
-    <row r="162" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A162" s="75">
         <v>44196</v>
       </c>
@@ -30741,7 +30741,7 @@
         <v>53621.390833180005</v>
       </c>
     </row>
-    <row r="163" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A163" s="75">
         <v>44225</v>
       </c>
@@ -30848,7 +30848,7 @@
         <v>55327.324897800005</v>
       </c>
     </row>
-    <row r="164" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A164" s="75">
         <v>44253</v>
       </c>
@@ -30955,7 +30955,7 @@
         <v>57852.396797460002</v>
       </c>
     </row>
-    <row r="165" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A165" s="75">
         <v>44286</v>
       </c>
@@ -31062,7 +31062,7 @@
         <v>62451.254507539998</v>
       </c>
     </row>
-    <row r="166" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A166" s="75">
         <v>44316</v>
       </c>
@@ -31169,7 +31169,7 @@
         <v>65474.233220150003</v>
       </c>
     </row>
-    <row r="167" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A167" s="75">
         <v>44347</v>
       </c>
@@ -31276,7 +31276,7 @@
         <v>64916.217841539998</v>
       </c>
     </row>
-    <row r="168" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A168" s="75">
         <v>44377</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>67259.850887780005</v>
       </c>
     </row>
-    <row r="169" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A169" s="75">
         <v>44407</v>
       </c>
@@ -31490,7 +31490,7 @@
         <v>68028.53398616999</v>
       </c>
     </row>
-    <row r="170" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A170" s="75">
         <v>44439</v>
       </c>
@@ -31597,7 +31597,7 @@
         <v>71923.246958570002</v>
       </c>
     </row>
-    <row r="171" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A171" s="75">
         <v>44469</v>
       </c>
@@ -31704,7 +31704,7 @@
         <v>72358.673868509999</v>
       </c>
     </row>
-    <row r="172" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A172" s="75">
         <v>44498</v>
       </c>
@@ -31811,7 +31811,7 @@
         <v>72928.336672770005</v>
       </c>
     </row>
-    <row r="173" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A173" s="75">
         <v>44530</v>
       </c>
@@ -31918,7 +31918,7 @@
         <v>71326.8168764</v>
       </c>
     </row>
-    <row r="174" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A174" s="75">
         <v>44561</v>
       </c>
@@ -32025,7 +32025,7 @@
         <v>73106.587637329998</v>
       </c>
     </row>
-    <row r="175" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A175" s="75">
         <v>44592</v>
       </c>
@@ -32132,7 +32132,7 @@
         <v>74053.448978850007</v>
       </c>
     </row>
-    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A176" s="75">
         <v>44620</v>
       </c>
@@ -32239,7 +32239,7 @@
         <v>74399.154679540006</v>
       </c>
     </row>
-    <row r="177" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A177" s="75">
         <v>44651</v>
       </c>
@@ -32346,7 +32346,7 @@
         <v>76249.250902009997</v>
       </c>
     </row>
-    <row r="178" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A178" s="75">
         <v>44680</v>
       </c>
@@ -32453,7 +32453,7 @@
         <v>72856.174017960002</v>
       </c>
     </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A179" s="75">
         <v>44712</v>
       </c>
@@ -32560,7 +32560,7 @@
         <v>77434.202898449992</v>
       </c>
     </row>
-    <row r="180" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A180" s="75">
         <v>44742</v>
       </c>
@@ -32667,7 +32667,7 @@
         <v>76493.946350590006</v>
       </c>
     </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A181" s="75">
         <v>44771</v>
       </c>
@@ -32775,7 +32775,7 @@
       </c>
       <c r="AJ181" s="88"/>
     </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A182" s="75">
         <v>44804</v>
       </c>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="AJ182" s="88"/>
     </row>
-    <row r="183" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A183" s="75">
         <v>44834</v>
       </c>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="AJ183" s="88"/>
     </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A184" s="75">
         <v>44865</v>
       </c>
@@ -33099,7 +33099,7 @@
       </c>
       <c r="AJ184" s="88"/>
     </row>
-    <row r="185" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A185" s="75">
         <v>44895</v>
       </c>
@@ -33207,7 +33207,7 @@
       </c>
       <c r="AJ185" s="88"/>
     </row>
-    <row r="186" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A186" s="75">
         <v>44925</v>
       </c>
@@ -33315,7 +33315,7 @@
       </c>
       <c r="AJ186" s="88"/>
     </row>
-    <row r="187" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A187" s="75">
         <v>44957</v>
       </c>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="AJ187" s="88"/>
     </row>
-    <row r="188" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A188" s="75">
         <v>44985</v>
       </c>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="AJ188" s="88"/>
     </row>
-    <row r="189" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A189" s="75">
         <v>45016</v>
       </c>
@@ -33639,7 +33639,7 @@
       </c>
       <c r="AJ189" s="88"/>
     </row>
-    <row r="190" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A190" s="75">
         <v>45044</v>
       </c>
@@ -33747,7 +33747,7 @@
       </c>
       <c r="AJ190" s="88"/>
     </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A191" s="75">
         <v>45077</v>
       </c>
@@ -33855,7 +33855,7 @@
       </c>
       <c r="AJ191" s="88"/>
     </row>
-    <row r="192" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A192" s="75">
         <v>45107</v>
       </c>
@@ -33963,7 +33963,7 @@
       </c>
       <c r="AJ192" s="88"/>
     </row>
-    <row r="193" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A193" s="75">
         <v>45138</v>
       </c>
@@ -34071,7 +34071,7 @@
       </c>
       <c r="AJ193" s="88"/>
     </row>
-    <row r="194" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A194" s="75">
         <v>45169</v>
       </c>
@@ -34178,7 +34178,7 @@
         <v>73264.329214569996</v>
       </c>
     </row>
-    <row r="195" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A195" s="75">
         <v>45198</v>
       </c>
@@ -34285,7 +34285,7 @@
         <v>72693.389935269995</v>
       </c>
     </row>
-    <row r="196" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A196" s="75">
         <v>45230</v>
       </c>
@@ -34392,7 +34392,7 @@
         <v>72998.857431080003</v>
       </c>
     </row>
-    <row r="197" spans="1:36" ht="13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A197" s="75">
         <v>45260</v>
       </c>
@@ -34499,7 +34499,7 @@
         <v>73308.217650089995</v>
       </c>
     </row>
-    <row r="198" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A198" s="75">
         <v>45289</v>
       </c>
@@ -34606,7 +34606,7 @@
         <v>69415.03949558</v>
       </c>
     </row>
-    <row r="199" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A199" s="75">
         <v>45322</v>
       </c>
@@ -34713,7 +34713,7 @@
         <v>69372.208303120002</v>
       </c>
     </row>
-    <row r="200" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A200" s="75">
         <v>45351</v>
       </c>
@@ -34820,7 +34820,7 @@
         <v>68545.833130170009</v>
       </c>
     </row>
-    <row r="201" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A201" s="75">
         <v>45380</v>
       </c>
@@ -34927,7 +34927,7 @@
         <v>69313.31956974999</v>
       </c>
     </row>
-    <row r="202" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A202" s="75">
         <v>45412</v>
       </c>
@@ -35034,7 +35034,7 @@
         <v>71530.887286429992</v>
       </c>
     </row>
-    <row r="203" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A203" s="75">
         <v>45443</v>
       </c>
@@ -35141,7 +35141,7 @@
         <v>62996.494070240005</v>
       </c>
     </row>
-    <row r="204" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A204" s="75">
         <v>45470</v>
       </c>
@@ -35248,7 +35248,7 @@
         <v>63636.916017880001</v>
       </c>
     </row>
-    <row r="205" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A205" s="75">
         <v>45504</v>
       </c>
@@ -35355,7 +35355,7 @@
         <v>64874.965348779995</v>
       </c>
     </row>
-    <row r="206" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A206" s="75">
         <v>45534</v>
       </c>
@@ -35462,7 +35462,7 @@
         <v>61566.668978069996</v>
       </c>
     </row>
-    <row r="207" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A207" s="75">
         <v>45565</v>
       </c>
@@ -35569,7 +35569,7 @@
         <v>59454.54697589</v>
       </c>
     </row>
-    <row r="208" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A208" s="75">
         <v>45596</v>
       </c>
@@ -35676,7 +35676,7 @@
         <v>64665.710123659999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A209" s="75">
         <v>45625</v>
       </c>
@@ -35783,7 +35783,7 @@
         <v>64030.552762779997</v>
       </c>
     </row>
-    <row r="210" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A210" s="75">
         <v>45657</v>
       </c>
@@ -35890,7 +35890,7 @@
         <v>60569.268901340001</v>
       </c>
     </row>
-    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A211" s="75">
         <v>45688</v>
       </c>
@@ -35997,7 +35997,7 @@
         <v>64706.023822700008</v>
       </c>
     </row>
-    <row r="212" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A212" s="75">
         <v>45716</v>
       </c>
@@ -36104,7 +36104,7 @@
         <v>64900.897019420001</v>
       </c>
     </row>
-    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A213" s="75">
         <v>45747</v>
       </c>
@@ -36211,7 +36211,7 @@
         <v>63785</v>
       </c>
     </row>
-    <row r="214" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A214" s="75">
         <v>45777</v>
       </c>
@@ -36318,7 +36318,7 @@
         <v>56305.50359986</v>
       </c>
     </row>
-    <row r="215" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A215" s="75">
         <v>45807</v>
       </c>
@@ -36425,7 +36425,7 @@
         <v>56558</v>
       </c>
     </row>
-    <row r="216" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A216" s="75">
         <v>45838</v>
       </c>
@@ -36532,7 +36532,7 @@
         <v>53271.850764169998</v>
       </c>
     </row>
-    <row r="217" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A217" s="75">
         <v>45869</v>
       </c>
@@ -36639,7 +36639,7 @@
         <v>54664</v>
       </c>
     </row>
-    <row r="218" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A218" s="75">
         <v>45898</v>
       </c>
@@ -36746,7 +36746,7 @@
         <v>51488</v>
       </c>
     </row>
-    <row r="219" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A219" s="75">
         <v>45930</v>
       </c>
@@ -36853,7 +36853,7 @@
         <v>53815</v>
       </c>
     </row>
-    <row r="220" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A220" s="75">
         <v>45961</v>
       </c>
@@ -36960,7 +36960,7 @@
         <v>49057.073048520004</v>
       </c>
     </row>
-    <row r="221" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A221" s="75">
         <v>45989</v>
       </c>
@@ -37067,7 +37067,7 @@
         <v>54669.470271930004</v>
       </c>
     </row>
-    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A222" s="75">
         <v>46022</v>
       </c>
@@ -37174,7 +37174,7 @@
         <v>51681.340129800003</v>
       </c>
     </row>
-    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A223" s="75">
         <v>46052</v>
       </c>
@@ -37281,7 +37281,7 @@
         <v>52830.0905231</v>
       </c>
     </row>
-    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A224" s="75">
         <v>46080</v>
       </c>
@@ -37388,7 +37388,7 @@
         <v>52174.252156579998</v>
       </c>
     </row>
-    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A225" s="75">
         <v>46112</v>
       </c>
@@ -37495,7 +37495,7 @@
         <v>56089.080521919997</v>
       </c>
     </row>
-    <row r="226" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A226" s="75">
         <v>46142</v>
       </c>
@@ -37602,7 +37602,7 @@
         <v>52503.768157110004</v>
       </c>
     </row>
-    <row r="227" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A227" s="75">
         <v>46171</v>
       </c>
@@ -37709,7 +37709,7 @@
         <v>52755</v>
       </c>
     </row>
-    <row r="228" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A228" s="75">
         <v>46203</v>
       </c>
@@ -37816,7 +37816,7 @@
         <v>52577</v>
       </c>
     </row>
-    <row r="229" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A229" s="75">
         <v>46234</v>
       </c>
@@ -37921,6 +37921,113 @@
       </c>
       <c r="AI229" s="5">
         <v>53803</v>
+      </c>
+    </row>
+    <row r="230" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A230" s="75">
+        <v>46265</v>
+      </c>
+      <c r="B230" s="5">
+        <v>25798.628520779999</v>
+      </c>
+      <c r="C230" s="5">
+        <v>-59.561302310001679</v>
+      </c>
+      <c r="D230" s="5">
+        <v>-767.17362151999964</v>
+      </c>
+      <c r="E230" s="5">
+        <v>-1270.6056079999998</v>
+      </c>
+      <c r="F230" s="5">
+        <v>0</v>
+      </c>
+      <c r="G230" s="5">
+        <v>-775.82585799999993</v>
+      </c>
+      <c r="H230" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I230" s="5">
+        <v>0</v>
+      </c>
+      <c r="J230" s="5">
+        <v>252.55735618</v>
+      </c>
+      <c r="K230" s="5">
+        <v>24178.019487129997</v>
+      </c>
+      <c r="L230" s="5">
+        <v>3522.181629480001</v>
+      </c>
+      <c r="M230" s="5">
+        <v>0</v>
+      </c>
+      <c r="N230" s="5">
+        <v>-4386.3738952899994</v>
+      </c>
+      <c r="O230" s="5">
+        <v>0</v>
+      </c>
+      <c r="P230" s="5">
+        <v>-1.7103700000014044E-3</v>
+      </c>
+      <c r="Q230" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="R230" s="5">
+        <v>2.6530157699999997</v>
+      </c>
+      <c r="S230" s="5">
+        <v>0</v>
+      </c>
+      <c r="T230" s="5">
+        <v>0</v>
+      </c>
+      <c r="U230" s="5">
+        <v>0</v>
+      </c>
+      <c r="V230" s="5">
+        <v>-861.54096040999832</v>
+      </c>
+      <c r="W230" s="5">
+        <v>23316.478526719999</v>
+      </c>
+      <c r="X230" s="5">
+        <v>26460</v>
+      </c>
+      <c r="Y230" s="5">
+        <v>11050.000000009999</v>
+      </c>
+      <c r="Z230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="5">
+        <v>30170</v>
+      </c>
+      <c r="AB230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD230" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG230" s="5">
+        <v>11388</v>
+      </c>
+      <c r="AH230" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI230" s="5">
+        <v>52608</v>
       </c>
     </row>
   </sheetData>
